--- a/backtest_runs/20260410_193731/by_symbol/GSPM/GSPM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GSPM/GSPM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>125445</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>125445</v>
@@ -955,7 +955,7 @@
         <v>-6361.25</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>119083.75</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>119083.75</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>119083.75</v>
@@ -1139,7 +1139,7 @@
         <v>-4071.200000000003</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>115012.55</v>
@@ -1185,7 +1185,7 @@
         <v>-7124.600000000007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>107887.95</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>107887.95</v>
@@ -1415,7 +1415,7 @@
         <v>-5343.449999999999</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>102544.5</v>
